--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prajo\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED6BB3A-4794-45F4-9507-A47220C25911}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A142E97C-00C9-4FFD-AA47-8A8934F6A697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,9 +190,6 @@
     <t>Satisfied</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>MCA/D1P2636</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
@@ -823,7 +823,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -893,7 +893,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -910,7 +910,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -918,7 +918,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -986,36 +986,36 @@
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="B6" s="9">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="C6" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D6" s="9">
         <v>120</v>
       </c>
       <c r="E6" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F6" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G6" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>885</v>
+        <v>960</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>555</v>
+        <v>480</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1024,10 +1024,10 @@
         <v>50</v>
       </c>
       <c r="M6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prajo\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A142E97C-00C9-4FFD-AA47-8A8934F6A697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -986,19 +986,19 @@
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46261</v>
+        <v>46245</v>
       </c>
       <c r="B6" s="9">
         <v>500</v>
       </c>
       <c r="C6" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" s="9">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E6" s="9">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F6" s="9">
         <v>200</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>960</v>
+        <v>880</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prajo\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A74DC5-20E5-484D-BF0D-4AEA2C115267}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -1031,25 +1037,47 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>200</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>700</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A74DC5-20E5-484D-BF0D-4AEA2C115267}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B46A7697-98FF-43D9-BE54-A6FEEDA7D7D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -492,6 +492,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1081,25 +1085,47 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="14">
+        <v>540</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14">
+        <v>50</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B46A7697-98FF-43D9-BE54-A6FEEDA7D7D6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6864EEF6-90F0-48F2-9F04-A9C766A1600A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1129,25 +1129,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="14">
+        <v>520</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6864EEF6-90F0-48F2-9F04-A9C766A1600A}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C76971C-28C2-42BD-8B32-CDE9ACB555EE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1173,25 +1179,47 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B10" s="14">
+        <v>600</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>500</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C76971C-28C2-42BD-8B32-CDE9ACB555EE}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F481059-25F6-4E3D-A206-F0420BD95858}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1223,25 +1223,47 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B11" s="14">
+        <v>600</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>400</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F481059-25F6-4E3D-A206-F0420BD95858}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE02D345-4930-457E-B4E6-28C33E6D8F01}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1267,25 +1267,47 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B12" s="14">
+        <v>500</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>320</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE02D345-4930-457E-B4E6-28C33E6D8F01}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFC0964-37F4-43AB-9B70-4A908B8B812D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1311,25 +1311,47 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="14">
+        <v>520</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>300</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFC0964-37F4-43AB-9B70-4A908B8B812D}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2820F6CF-F23B-40CC-B8BE-C66F2E3AE43D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1355,25 +1355,47 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="14">
+        <v>520</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>100</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2820F6CF-F23B-40CC-B8BE-C66F2E3AE43D}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0A6BE5-734C-474C-8BDF-02B8D0B82B4A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1399,25 +1399,47 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="14">
+        <v>520</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>150</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="14">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0A6BE5-734C-474C-8BDF-02B8D0B82B4A}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F629DF60-C1BC-499D-B088-EF8F872BE10B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1443,25 +1443,47 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="14">
+        <v>520</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F629DF60-C1BC-499D-B088-EF8F872BE10B}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB3DB60-FF01-442F-A98B-963882D53943}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1487,25 +1490,47 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="14">
+        <v>600</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>100</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB3DB60-FF01-442F-A98B-963882D53943}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF0205A-9273-4292-8CBE-7AD440361F0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1534,179 +1537,355 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="14">
+        <v>600</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>100</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="14">
+        <v>520</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>90</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="14">
+        <v>520</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="14">
+        <v>520</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>80</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="14">
+        <v>520</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>90</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="14">
+        <v>520</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>90</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>100</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="14">
+        <v>600</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>90</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>90</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>200</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF0205A-9273-4292-8CBE-7AD440361F0B}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63287E4E-EEFD-4DBD-8F5A-69F0FA3F796C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1889,25 +1889,47 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="14">
+        <v>520</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>90</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63287E4E-EEFD-4DBD-8F5A-69F0FA3F796C}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C44B94B4-128F-4A2F-9B4F-5CFB85AAEF2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1933,47 +1933,91 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B27" s="14">
+        <v>520</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B28" s="14">
+        <v>520</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C44B94B4-128F-4A2F-9B4F-5CFB85AAEF2F}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7BE8BD-23D7-4C75-A8C7-360C73BDCFD7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2021,25 +2021,47 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="14">
+        <v>520</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7BE8BD-23D7-4C75-A8C7-360C73BDCFD7}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B62574-A6C6-4710-A454-9838C905E218}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2065,25 +2065,47 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="14">
+        <v>520</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>50</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
